--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>303649</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>21.7600002288818</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>22.1599998474121</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>21.7600002288818</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>139424</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>21.9200000762939</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>21.4400005340576</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>21.7199993133545</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>162612</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>22.1200008392334</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>22.0400009155273</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>175538</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>22.5599994659424</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>21.8199996948242</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>21.8199996948242</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>22.5599994659424</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>193883</v>
+        <v>126232</v>
       </c>
       <c r="C2715" t="n">
-        <v>22.7199993133545</v>
+        <v>22.5200004577637</v>
       </c>
       <c r="D2715" t="n">
-        <v>22.2199993133545</v>
+        <v>22.2600002288818</v>
       </c>
       <c r="E2715" t="n">
-        <v>22.3999996185303</v>
+        <v>22.2800006866455</v>
       </c>
       <c r="F2715" t="n">
-        <v>22.5400009155273</v>
+        <v>22.2800006866455</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>159408</v>
+        <v>193883</v>
       </c>
       <c r="C2716" t="n">
-        <v>22.6599998474121</v>
+        <v>22.7199993133545</v>
       </c>
       <c r="D2716" t="n">
-        <v>22.1399993896484</v>
+        <v>22.2199993133545</v>
       </c>
       <c r="E2716" t="n">
-        <v>22.5599994659424</v>
+        <v>22.3999996185303</v>
       </c>
       <c r="F2716" t="n">
-        <v>22.1599998474121</v>
+        <v>22.5400009155273</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>132883</v>
+        <v>159408</v>
       </c>
       <c r="C2717" t="n">
-        <v>22.3799991607666</v>
+        <v>22.6599998474121</v>
       </c>
       <c r="D2717" t="n">
-        <v>22.0599994659424</v>
+        <v>22.1399993896484</v>
       </c>
       <c r="E2717" t="n">
-        <v>22.1000003814697</v>
+        <v>22.5599994659424</v>
       </c>
       <c r="F2717" t="n">
-        <v>22.0599994659424</v>
+        <v>22.1599998474121</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>189801</v>
+        <v>132883</v>
       </c>
       <c r="C2718" t="n">
-        <v>22.5</v>
+        <v>22.3799991607666</v>
       </c>
       <c r="D2718" t="n">
-        <v>22.0400009155273</v>
+        <v>22.0599994659424</v>
       </c>
       <c r="E2718" t="n">
-        <v>22.3600006103516</v>
+        <v>22.1000003814697</v>
       </c>
       <c r="F2718" t="n">
-        <v>22.2199993133545</v>
+        <v>22.0599994659424</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>303649</v>
+        <v>189801</v>
       </c>
       <c r="C2719" t="n">
-        <v>22.2000007629395</v>
+        <v>22.5</v>
       </c>
       <c r="D2719" t="n">
-        <v>21.7600002288818</v>
+        <v>22.0400009155273</v>
       </c>
       <c r="E2719" t="n">
-        <v>22.1599998474121</v>
+        <v>22.3600006103516</v>
       </c>
       <c r="F2719" t="n">
-        <v>21.7600002288818</v>
+        <v>22.2199993133545</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>139424</v>
+        <v>303649</v>
       </c>
       <c r="C2720" t="n">
-        <v>21.9200000762939</v>
+        <v>22.2000007629395</v>
       </c>
       <c r="D2720" t="n">
-        <v>21.4400005340576</v>
+        <v>21.7600002288818</v>
       </c>
       <c r="E2720" t="n">
-        <v>21.7000007629395</v>
+        <v>22.1599998474121</v>
       </c>
       <c r="F2720" t="n">
-        <v>21.7199993133545</v>
+        <v>21.7600002288818</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>162612</v>
+        <v>139424</v>
       </c>
       <c r="C2721" t="n">
-        <v>22.1200008392334</v>
+        <v>21.9200000762939</v>
       </c>
       <c r="D2721" t="n">
-        <v>21.6000003814697</v>
+        <v>21.4400005340576</v>
       </c>
       <c r="E2721" t="n">
-        <v>21.6000003814697</v>
+        <v>21.7000007629395</v>
       </c>
       <c r="F2721" t="n">
-        <v>22.0400009155273</v>
+        <v>21.7199993133545</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>175538</v>
+        <v>162612</v>
       </c>
       <c r="C2722" t="n">
+        <v>22.1200008392334</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>22.0400009155273</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>462351</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>22.7399997711182</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>22.3400001525879</v>
+      </c>
+      <c r="E2723" t="n">
         <v>22.5599994659424</v>
       </c>
-      <c r="D2722" t="n">
-        <v>21.8199996948242</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>21.8199996948242</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>22.5599994659424</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>22.6399993896484</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>22.4599990844727</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>22.2399997711182</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>106533</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>22.2399997711182</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>22.2399997711182</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>22.2399997711182</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>22.3600006103516</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>106333</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>22.4799995422363</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>22.1200008392334</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>22.2199993133545</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>22.2199993133545</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>22.1800003051758</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>175747</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>22.3799991607666</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>21.8799991607666</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>22.1599998474121</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>22.1599998474121</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>22.0799999237061</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>94091</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>22.3400001525879</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>22.2600002288818</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>81537</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>22.0799999237061</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>22.0799999237061</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>7.16729879379272</v>
+        <v>7.1673002243042</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>7.12075901031494</v>
+        <v>7.12075853347778</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>6.74261474609375</v>
+        <v>6.74261379241943</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G6" t="n">
-        <v>6.69607353210449</v>
+        <v>6.69607400894165</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G8" t="n">
-        <v>6.94041347503662</v>
+        <v>6.9404125213623</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G9" t="n">
-        <v>6.91132545471191</v>
+        <v>6.9113245010376</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8647837638855</v>
+        <v>6.86478424072266</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G11" t="n">
-        <v>6.77170181274414</v>
+        <v>6.77170276641846</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.25</v>
       </c>
       <c r="G15" t="n">
-        <v>6.54481554031372</v>
+        <v>6.5448145866394</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>6.67280292510986</v>
+        <v>6.67280387878418</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G17" t="n">
-        <v>6.77170181274414</v>
+        <v>6.77170276641846</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G19" t="n">
-        <v>6.70770740509033</v>
+        <v>6.70770835876465</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.69025611877441</v>
+        <v>6.6902551651001</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G22" t="n">
-        <v>6.70770740509033</v>
+        <v>6.70770835876465</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>6.63208055496216</v>
+        <v>6.63207912445068</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>6.56808614730835</v>
+        <v>6.56808567047119</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.25</v>
       </c>
       <c r="G25" t="n">
-        <v>6.54481554031372</v>
+        <v>6.5448145866394</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>6.63208055496216</v>
+        <v>6.63207912445068</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G28" t="n">
-        <v>6.20157527923584</v>
+        <v>6.20157718658447</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G31" t="n">
-        <v>6.48663949966431</v>
+        <v>6.48663759231567</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G32" t="n">
-        <v>6.643714427948</v>
+        <v>6.64371490478516</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G33" t="n">
-        <v>6.57972002029419</v>
+        <v>6.57972097396851</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G34" t="n">
-        <v>6.643714427948</v>
+        <v>6.64371490478516</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G35" t="n">
-        <v>6.56808614730835</v>
+        <v>6.56808567047119</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G36" t="n">
-        <v>6.34701585769653</v>
+        <v>6.34701633453369</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G37" t="n">
-        <v>6.49827480316162</v>
+        <v>6.49827432632446</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G38" t="n">
-        <v>6.30047512054443</v>
+        <v>6.30047607421875</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>6.42846345901489</v>
+        <v>6.42846393585205</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>6.48663949966431</v>
+        <v>6.48663759231567</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.25</v>
       </c>
       <c r="G42" t="n">
-        <v>6.54481554031372</v>
+        <v>6.5448145866394</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>6.51572704315186</v>
+        <v>6.5157265663147</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>6.48663949966431</v>
+        <v>6.48663759231567</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>6.55063438415527</v>
+        <v>6.55063247680664</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G47" t="n">
-        <v>6.53899717330933</v>
+        <v>6.53899812698364</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G48" t="n">
-        <v>6.58553791046143</v>
+        <v>6.58553886413574</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>6.48663949966431</v>
+        <v>6.48663759231567</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>6.45755052566528</v>
+        <v>6.45755195617676</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>6.74843120574951</v>
+        <v>6.74843168258667</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.25</v>
       </c>
       <c r="G58" t="n">
-        <v>6.54481554031372</v>
+        <v>6.5448145866394</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G60" t="n">
-        <v>7.04513025283813</v>
+        <v>7.04512977600098</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G61" t="n">
-        <v>7.0334939956665</v>
+        <v>7.03349590301514</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G62" t="n">
-        <v>7.0334939956665</v>
+        <v>7.03349590301514</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G63" t="n">
-        <v>6.9578652381897</v>
+        <v>6.95786571502686</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G64" t="n">
-        <v>6.91714143753052</v>
+        <v>6.91714286804199</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>6.80660772323608</v>
+        <v>6.80660820007324</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.5</v>
       </c>
       <c r="G66" t="n">
-        <v>6.69025611877441</v>
+        <v>6.6902551651001</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G67" t="n">
-        <v>6.69607353210449</v>
+        <v>6.69607400894165</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G68" t="n">
-        <v>6.67280292510986</v>
+        <v>6.67280387878418</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>6.73097991943359</v>
+        <v>6.73097848892212</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>6.77752017974854</v>
+        <v>6.77751970291138</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G71" t="n">
-        <v>6.75425004959106</v>
+        <v>6.75424957275391</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>6.88223695755005</v>
+        <v>6.88223648071289</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>6.92296028137207</v>
+        <v>6.92295932769775</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G74" t="n">
-        <v>6.84733247756958</v>
+        <v>6.84733200073242</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G76" t="n">
-        <v>6.85896682739258</v>
+        <v>6.85896587371826</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G77" t="n">
-        <v>6.69607353210449</v>
+        <v>6.69607400894165</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>6.53899717330933</v>
+        <v>6.53899812698364</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>6.66116762161255</v>
+        <v>6.66116714477539</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G83" t="n">
-        <v>6.63789653778076</v>
+        <v>6.63789701461792</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G85" t="n">
-        <v>6.67280292510986</v>
+        <v>6.67280387878418</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G87" t="n">
-        <v>6.57972002029419</v>
+        <v>6.57972097396851</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G88" t="n">
-        <v>6.66698455810547</v>
+        <v>6.66698503494263</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G89" t="n">
-        <v>6.53899717330933</v>
+        <v>6.53899812698364</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G91" t="n">
-        <v>6.58553791046143</v>
+        <v>6.58553886413574</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>6.53899717330933</v>
+        <v>6.53899812698364</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>6.66116762161255</v>
+        <v>6.66116714477539</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G95" t="n">
-        <v>6.88223695755005</v>
+        <v>6.88223648071289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.75</v>
       </c>
       <c r="G96" t="n">
-        <v>6.83569622039795</v>
+        <v>6.83569526672363</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>6.80660772323608</v>
+        <v>6.80660820007324</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G99" t="n">
-        <v>6.67280292510986</v>
+        <v>6.67280387878418</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>10.75</v>
       </c>
       <c r="G100" t="n">
-        <v>6.8512544631958</v>
+        <v>6.85125398635864</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>6.99783754348755</v>
+        <v>6.99783897399902</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>6.94685316085815</v>
+        <v>6.94685220718384</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G104" t="n">
-        <v>7.0297064781189</v>
+        <v>7.02970552444458</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>6.94047880172729</v>
+        <v>6.94047975540161</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G108" t="n">
-        <v>6.90861463546753</v>
+        <v>6.90861320495605</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G109" t="n">
-        <v>6.92136001586914</v>
+        <v>6.92135906219482</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>6.91498804092407</v>
+        <v>6.91498708724976</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G113" t="n">
-        <v>6.90861463546753</v>
+        <v>6.90861320495605</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>6.80026817321777</v>
+        <v>6.80026769638062</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="G116" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>6.32227373123169</v>
+        <v>6.32227230072021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>6.22986030578613</v>
+        <v>6.22986078262329</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>6.66005563735962</v>
+        <v>6.66005754470825</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>10.25</v>
       </c>
       <c r="G122" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>6.58995008468628</v>
+        <v>6.58994960784912</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G124" t="n">
-        <v>6.20118093490601</v>
+        <v>6.20118045806885</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.49499988555908</v>
       </c>
       <c r="G125" t="n">
-        <v>6.05141115188599</v>
+        <v>6.05141067504883</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.40512609481812</v>
+        <v>6.4051251411438</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G129" t="n">
-        <v>6.62181663513184</v>
+        <v>6.62181711196899</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>6.73653554916382</v>
+        <v>6.73653507232666</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G133" t="n">
-        <v>6.33501863479614</v>
+        <v>6.33502006530762</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>6.43061923980713</v>
+        <v>6.43061876296997</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G135" t="n">
-        <v>6.39875221252441</v>
+        <v>6.39875268936157</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G136" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.25</v>
       </c>
       <c r="G137" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G138" t="n">
-        <v>6.58357763290405</v>
+        <v>6.58357715606689</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G139" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G140" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G144" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>6.47523212432861</v>
+        <v>6.47523164749146</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G147" t="n">
-        <v>6.57083129882812</v>
+        <v>6.57083034515381</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>6.481605052948</v>
+        <v>6.48160409927368</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>6.59632349014282</v>
+        <v>6.59632396697998</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G150" t="n">
-        <v>6.4433650970459</v>
+        <v>6.44336557388306</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G151" t="n">
-        <v>6.36051273345947</v>
+        <v>6.36051321029663</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G154" t="n">
-        <v>6.53896427154541</v>
+        <v>6.53896379470825</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G155" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G156" t="n">
-        <v>6.53896427154541</v>
+        <v>6.53896379470825</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10.25</v>
       </c>
       <c r="G157" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G158" t="n">
-        <v>6.63456249237061</v>
+        <v>6.63456296920776</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G159" t="n">
-        <v>6.66642904281616</v>
+        <v>6.66642951965332</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G160" t="n">
-        <v>6.63456249237061</v>
+        <v>6.63456296920776</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G161" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G162" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G164" t="n">
-        <v>6.42424583435059</v>
+        <v>6.42424535751343</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G166" t="n">
-        <v>6.43061923980713</v>
+        <v>6.43061876296997</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>6.36688613891602</v>
+        <v>6.36688566207886</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>6.34458017349243</v>
+        <v>6.34457969665527</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>6.35732698440552</v>
+        <v>6.35732650756836</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10</v>
       </c>
       <c r="G171" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G172" t="n">
-        <v>6.66005563735962</v>
+        <v>6.66005754470825</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G173" t="n">
-        <v>6.71741485595703</v>
+        <v>6.71741628646851</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G174" t="n">
-        <v>6.73653554916382</v>
+        <v>6.73653507232666</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G176" t="n">
-        <v>6.71104288101196</v>
+        <v>6.71104335784912</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G177" t="n">
-        <v>6.7429084777832</v>
+        <v>6.74290943145752</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G178" t="n">
-        <v>6.86400127410889</v>
+        <v>6.86400032043457</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G179" t="n">
-        <v>6.62181663513184</v>
+        <v>6.62181711196899</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>6.57720470428467</v>
+        <v>6.57720375061035</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>6.62819004058838</v>
+        <v>6.6281909942627</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G182" t="n">
-        <v>6.67917633056641</v>
+        <v>6.67917585372925</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G183" t="n">
-        <v>6.54533815383911</v>
+        <v>6.54533767700195</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G184" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G185" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G186" t="n">
-        <v>6.481605052948</v>
+        <v>6.48160409927368</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G188" t="n">
-        <v>6.58995008468628</v>
+        <v>6.58994960784912</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G190" t="n">
-        <v>6.4433650970459</v>
+        <v>6.44336557388306</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.25</v>
       </c>
       <c r="G192" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G193" t="n">
-        <v>6.50709772109985</v>
+        <v>6.50709676742554</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G195" t="n">
-        <v>6.481605052948</v>
+        <v>6.48160409927368</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G197" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10</v>
       </c>
       <c r="G198" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G201" t="n">
-        <v>6.27128791809082</v>
+        <v>6.27128744125366</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10</v>
       </c>
       <c r="G202" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G205" t="n">
-        <v>6.37963390350342</v>
+        <v>6.37963247299194</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G206" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>6.58995008468628</v>
+        <v>6.58994960784912</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59632349014282</v>
+        <v>6.59632396697998</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G214" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G215" t="n">
-        <v>6.42424583435059</v>
+        <v>6.42424535751343</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>6.3254599571228</v>
+        <v>6.32545948028564</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G218" t="n">
-        <v>6.18206167221069</v>
+        <v>6.18206119537354</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37007284164429</v>
+        <v>6.3700737953186</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G220" t="n">
-        <v>6.39238023757935</v>
+        <v>6.39237928390503</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>6.18843507766724</v>
+        <v>6.18843555450439</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>5.876145362854</v>
+        <v>5.87614583969116</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G223" t="n">
-        <v>5.96218395233154</v>
+        <v>5.96218347549438</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>5.92713165283203</v>
+        <v>5.92713260650635</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>5.98130416870117</v>
+        <v>5.98130321502686</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G227" t="n">
-        <v>5.87295818328857</v>
+        <v>5.87295913696289</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G228" t="n">
-        <v>5.80603981018066</v>
+        <v>5.80603933334351</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G229" t="n">
-        <v>5.876145362854</v>
+        <v>5.87614583969116</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G230" t="n">
-        <v>5.90482616424561</v>
+        <v>5.90482521057129</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>5.87933254241943</v>
+        <v>5.87933206558228</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G234" t="n">
-        <v>5.78054666519165</v>
+        <v>5.78054571151733</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.84746599197388</v>
+        <v>5.84746646881104</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G241" t="n">
-        <v>5.96537113189697</v>
+        <v>5.96537017822266</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G243" t="n">
-        <v>5.95581150054932</v>
+        <v>5.95581197738647</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>5.95262479782104</v>
+        <v>5.95262384414673</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G245" t="n">
-        <v>6.0864634513855</v>
+        <v>6.08646297454834</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G247" t="n">
-        <v>6.18206167221069</v>
+        <v>6.18206119537354</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>6.341392993927</v>
+        <v>6.34139251708984</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>6.341392993927</v>
+        <v>6.34139251708984</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10</v>
       </c>
       <c r="G250" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>6.36688613891602</v>
+        <v>6.36688566207886</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="G252" t="n">
-        <v>6.37326002120972</v>
+        <v>6.37325859069824</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>6.4178729057312</v>
+        <v>6.41787147521973</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G255" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G256" t="n">
-        <v>6.50709772109985</v>
+        <v>6.50709676742554</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G258" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.25</v>
       </c>
       <c r="G259" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.25</v>
       </c>
       <c r="G260" t="n">
-        <v>6.53259229660034</v>
+        <v>6.53259134292603</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G261" t="n">
-        <v>6.54533815383911</v>
+        <v>6.54533767700195</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G262" t="n">
-        <v>6.55808401107788</v>
+        <v>6.55808305740356</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G263" t="n">
-        <v>6.41149806976318</v>
+        <v>6.41150045394897</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G264" t="n">
-        <v>6.42424583435059</v>
+        <v>6.42424535751343</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G265" t="n">
-        <v>6.4497389793396</v>
+        <v>6.44973754882812</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G266" t="n">
-        <v>6.51984453201294</v>
+        <v>6.51984405517578</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G268" t="n">
-        <v>6.5134711265564</v>
+        <v>6.51347160339355</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>6.59632349014282</v>
+        <v>6.59632396697998</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.5</v>
       </c>
       <c r="G274" t="n">
-        <v>6.69192171096802</v>
+        <v>6.69192314147949</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G276" t="n">
-        <v>6.73653554916382</v>
+        <v>6.73653507232666</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>6.66005563735962</v>
+        <v>6.66005754470825</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G278" t="n">
-        <v>6.55808401107788</v>
+        <v>6.55808305740356</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G279" t="n">
-        <v>6.54533815383911</v>
+        <v>6.54533767700195</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G280" t="n">
-        <v>6.53896427154541</v>
+        <v>6.53896379470825</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G283" t="n">
-        <v>6.61544322967529</v>
+        <v>6.61544418334961</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G284" t="n">
-        <v>6.61544322967529</v>
+        <v>6.61544418334961</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>6.62181663513184</v>
+        <v>6.62181711196899</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G286" t="n">
-        <v>6.62819004058838</v>
+        <v>6.6281909942627</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>6.55808401107788</v>
+        <v>6.55808305740356</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G289" t="n">
-        <v>6.76840162277222</v>
+        <v>6.76840209960938</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G290" t="n">
-        <v>6.82576036453247</v>
+        <v>6.82576179504395</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>6.84488010406494</v>
+        <v>6.84488153457642</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G293" t="n">
-        <v>6.8767466545105</v>
+        <v>6.87674760818481</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G294" t="n">
-        <v>6.79389476776123</v>
+        <v>6.79389524459839</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G295" t="n">
-        <v>6.80026817321777</v>
+        <v>6.80026769638062</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G296" t="n">
-        <v>6.79389476776123</v>
+        <v>6.79389524459839</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G297" t="n">
-        <v>6.74928045272827</v>
+        <v>6.7492823600769</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>6.84488010406494</v>
+        <v>6.84488153457642</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G299" t="n">
-        <v>6.99783754348755</v>
+        <v>6.99783897399902</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>6.95960092544556</v>
+        <v>6.95959901809692</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G302" t="n">
-        <v>6.97234630584717</v>
+        <v>6.97234487533569</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>6.95960092544556</v>
+        <v>6.95959901809692</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G304" t="n">
-        <v>6.99146604537964</v>
+        <v>6.99146509170532</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G305" t="n">
-        <v>6.90861463546753</v>
+        <v>6.90861320495605</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>11</v>
       </c>
       <c r="G307" t="n">
-        <v>7.01058578491211</v>
+        <v>7.01058626174927</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G308" t="n">
-        <v>7.00421142578125</v>
+        <v>7.00421094894409</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G309" t="n">
-        <v>6.95960092544556</v>
+        <v>6.95959901809692</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G310" t="n">
-        <v>7.0297064781189</v>
+        <v>7.02970552444458</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G311" t="n">
-        <v>7.04882574081421</v>
+        <v>7.04882478713989</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G312" t="n">
-        <v>7.19540929794312</v>
+        <v>7.19541025161743</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.26551628112793</v>
+        <v>7.26551580429077</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G314" t="n">
-        <v>7.2782621383667</v>
+        <v>7.27826356887817</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G315" t="n">
-        <v>7.3802342414856</v>
+        <v>7.38023567199707</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G317" t="n">
-        <v>7.44396686553955</v>
+        <v>7.44396781921387</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G318" t="n">
-        <v>7.40572738647461</v>
+        <v>7.40572690963745</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>7.45671415328979</v>
+        <v>7.45671319961548</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>7.4248480796814</v>
+        <v>7.42484712600708</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>11.75</v>
       </c>
       <c r="G321" t="n">
-        <v>7.48857975006104</v>
+        <v>7.48858022689819</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>7.53956604003906</v>
+        <v>7.53956508636475</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G325" t="n">
-        <v>7.56505870819092</v>
+        <v>7.56506013870239</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G327" t="n">
-        <v>7.6096715927124</v>
+        <v>7.60967206954956</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>7.58417797088623</v>
+        <v>7.58417892456055</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G329" t="n">
-        <v>7.62241792678833</v>
+        <v>7.62241840362549</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G330" t="n">
-        <v>7.58417797088623</v>
+        <v>7.58417892456055</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>7.39298152923584</v>
+        <v>7.392982006073</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>7.29738330841064</v>
+        <v>7.29738187789917</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G334" t="n">
-        <v>7.2209038734436</v>
+        <v>7.22090291976929</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G336" t="n">
-        <v>7.31012916564941</v>
+        <v>7.31012964248657</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>7.2782621383667</v>
+        <v>7.27826356887817</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>7.26551628112793</v>
+        <v>7.26551580429077</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G341" t="n">
-        <v>7.31012916564941</v>
+        <v>7.31012964248657</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G342" t="n">
-        <v>7.2463960647583</v>
+        <v>7.24639654159546</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>7.44396686553955</v>
+        <v>7.44396781921387</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G344" t="n">
-        <v>7.41210126876831</v>
+        <v>7.41210174560547</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G345" t="n">
-        <v>7.44396686553955</v>
+        <v>7.44396781921387</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G346" t="n">
-        <v>7.40572738647461</v>
+        <v>7.40572690963745</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>7.46945905685425</v>
+        <v>7.46946001052856</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G348" t="n">
-        <v>7.46945905685425</v>
+        <v>7.46946001052856</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G349" t="n">
-        <v>7.55868625640869</v>
+        <v>7.55868530273438</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>7.58417797088623</v>
+        <v>7.58417892456055</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>7.62241792678833</v>
+        <v>7.62241840362549</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>7.60329866409302</v>
+        <v>7.60329818725586</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>7.51407241821289</v>
+        <v>7.51407337188721</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>7.72439098358154</v>
+        <v>7.72439050674438</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G355" t="n">
-        <v>7.85734081268311</v>
+        <v>7.85733985900879</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G356" t="n">
-        <v>7.89722633361816</v>
+        <v>7.89722490310669</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>7.87728404998779</v>
+        <v>7.87728309631348</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G358" t="n">
-        <v>7.96369934082031</v>
+        <v>7.96370029449463</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>7.99693822860718</v>
+        <v>7.99693727493286</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>7.93046236038208</v>
+        <v>7.93046283721924</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>8.01688098907471</v>
+        <v>8.01687908172607</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99029159545898</v>
+        <v>7.99029064178467</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>8.03017425537109</v>
+        <v>8.03017520904541</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>8.09000205993652</v>
+        <v>8.09000301361084</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>8.36255073547363</v>
+        <v>8.36254978179932</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G372" t="n">
-        <v>8.29607486724854</v>
+        <v>8.29607391357422</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>12.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.30937099456787</v>
+        <v>8.30937004089355</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G377" t="n">
-        <v>8.32266616821289</v>
+        <v>8.32266521453857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.24289512634277</v>
+        <v>8.24289417266846</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.25</v>
       </c>
       <c r="G379" t="n">
-        <v>8.14318180084229</v>
+        <v>8.1431827545166</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G380" t="n">
-        <v>8.22295188903809</v>
+        <v>8.2229528427124</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.25</v>
       </c>
       <c r="G381" t="n">
-        <v>8.14318180084229</v>
+        <v>8.1431827545166</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G382" t="n">
-        <v>8.16312599182129</v>
+        <v>8.16312503814697</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>12.25</v>
       </c>
       <c r="G383" t="n">
-        <v>8.14318180084229</v>
+        <v>8.1431827545166</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G384" t="n">
-        <v>8.18306827545166</v>
+        <v>8.18306732177734</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>12.25</v>
       </c>
       <c r="G386" t="n">
-        <v>8.14318180084229</v>
+        <v>8.1431827545166</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G387" t="n">
-        <v>8.14983081817627</v>
+        <v>8.14982986450195</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G388" t="n">
-        <v>8.10329914093018</v>
+        <v>8.10329723358154</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>8.10994338989258</v>
+        <v>8.10994529724121</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>8.16312599182129</v>
+        <v>8.16312503814697</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G391" t="n">
-        <v>8.24954223632812</v>
+        <v>8.24954319000244</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G392" t="n">
-        <v>8.29607486724854</v>
+        <v>8.29607391357422</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G393" t="n">
-        <v>8.29607486724854</v>
+        <v>8.29607391357422</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G394" t="n">
-        <v>8.28942680358887</v>
+        <v>8.28942775726318</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>8.28942680358887</v>
+        <v>8.28942775726318</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>8.27613162994385</v>
+        <v>8.27613258361816</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>8.22295188903809</v>
+        <v>8.2229528427124</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>8.10329914093018</v>
+        <v>8.10329723358154</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G400" t="n">
-        <v>8.03017425537109</v>
+        <v>8.03017520904541</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G402" t="n">
-        <v>8.07005977630615</v>
+        <v>8.07006072998047</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G405" t="n">
-        <v>8.03017425537109</v>
+        <v>8.03017520904541</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17642021179199</v>
+        <v>8.17641925811768</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>8.2096586227417</v>
+        <v>8.20965671539307</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>8.2096586227417</v>
+        <v>8.20965671539307</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G409" t="n">
-        <v>8.23624801635742</v>
+        <v>8.23624706268311</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G410" t="n">
-        <v>8.18306827545166</v>
+        <v>8.18306732177734</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>8.2096586227417</v>
+        <v>8.20965671539307</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>8.16312599182129</v>
+        <v>8.16312503814697</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>8.34260940551758</v>
+        <v>8.34260845184326</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>8.61515522003174</v>
+        <v>8.61515617370605</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>8.76139831542969</v>
+        <v>8.76140117645264</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G417" t="n">
-        <v>8.76139831542969</v>
+        <v>8.76140117645264</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>8.74145793914795</v>
+        <v>8.74145603179932</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G419" t="n">
-        <v>8.6816291809082</v>
+        <v>8.68163108825684</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G420" t="n">
-        <v>8.76139831542969</v>
+        <v>8.76140117645264</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.74145793914795</v>
+        <v>8.74145603179932</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>8.6816291809082</v>
+        <v>8.68163108825684</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G423" t="n">
-        <v>8.70157241821289</v>
+        <v>8.70157337188721</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G424" t="n">
-        <v>8.62180137634277</v>
+        <v>8.62180328369141</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G425" t="n">
-        <v>8.57526969909668</v>
+        <v>8.57526874542236</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G427" t="n">
-        <v>8.76139831542969</v>
+        <v>8.76140117645264</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G428" t="n">
-        <v>8.73480892181396</v>
+        <v>8.73480987548828</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G429" t="n">
-        <v>8.8145809173584</v>
+        <v>8.81457996368408</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G432" t="n">
-        <v>8.90099811553955</v>
+        <v>8.90099716186523</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G435" t="n">
-        <v>9.01400470733643</v>
+        <v>9.01400566101074</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G438" t="n">
-        <v>8.91429138183594</v>
+        <v>8.91429328918457</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G439" t="n">
-        <v>8.91429138183594</v>
+        <v>8.91429328918457</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>9.04724216461182</v>
+        <v>9.0472412109375</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>9.04059410095215</v>
+        <v>9.04059505462646</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G444" t="n">
-        <v>9.04724216461182</v>
+        <v>9.0472412109375</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>9.00070858001709</v>
+        <v>9.00070953369141</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G446" t="n">
-        <v>8.98741436004639</v>
+        <v>8.9874153137207</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G447" t="n">
-        <v>9.00070858001709</v>
+        <v>9.00070953369141</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G449" t="n">
-        <v>9.04724216461182</v>
+        <v>9.0472412109375</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G451" t="n">
-        <v>9.00070858001709</v>
+        <v>9.00070953369141</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G453" t="n">
-        <v>8.94753074645996</v>
+        <v>8.94752883911133</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G454" t="n">
-        <v>8.92094039916992</v>
+        <v>8.92093944549561</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G457" t="n">
-        <v>9.33308506011963</v>
+        <v>9.33308410644531</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>9.37296867370605</v>
+        <v>9.37297058105469</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37296867370605</v>
+        <v>9.37297058105469</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G461" t="n">
-        <v>9.38626384735107</v>
+        <v>9.38626480102539</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G464" t="n">
-        <v>9.35302734375</v>
+        <v>9.35302639007568</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G465" t="n">
-        <v>9.34637928009033</v>
+        <v>9.34638023376465</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>9.32643604278564</v>
+        <v>9.32643795013428</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>9.53915691375732</v>
+        <v>9.53915882110596</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G468" t="n">
-        <v>9.59898376464844</v>
+        <v>9.59898471832275</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>9.51256656646729</v>
+        <v>9.51256561279297</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G470" t="n">
-        <v>9.53915691375732</v>
+        <v>9.53915882110596</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>9.75187587738037</v>
+        <v>9.75187683105469</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G475" t="n">
-        <v>10.0510139465332</v>
+        <v>10.0510129928589</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>10.1174879074097</v>
+        <v>10.117488861084</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G478" t="n">
-        <v>9.95130157470703</v>
+        <v>9.95130062103271</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G482" t="n">
-        <v>10.1108427047729</v>
+        <v>10.1108407974243</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G483" t="n">
-        <v>10.1706705093384</v>
+        <v>10.1706686019897</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G485" t="n">
-        <v>10.2437915802002</v>
+        <v>10.2437906265259</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3169145584106</v>
+        <v>10.3169136047363</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G490" t="n">
-        <v>10.6160507202148</v>
+        <v>10.6160516738892</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>10.3169145584106</v>
+        <v>10.3169136047363</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G496" t="n">
-        <v>10.4764547348022</v>
+        <v>10.4764537811279</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>10.6027555465698</v>
+        <v>10.6027574539185</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G499" t="n">
-        <v>10.9085416793823</v>
+        <v>10.9085397720337</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G501" t="n">
-        <v>10.6758794784546</v>
+        <v>10.675877571106</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>10.5894622802734</v>
+        <v>10.5894613265991</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>10.7357063293457</v>
+        <v>10.7357053756714</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G504" t="n">
-        <v>10.8287706375122</v>
+        <v>10.8287715911865</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G505" t="n">
-        <v>10.7556486129761</v>
+        <v>10.7556495666504</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G506" t="n">
-        <v>10.7290573120117</v>
+        <v>10.729058265686</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>10.2770280838013</v>
+        <v>10.2770299911499</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G510" t="n">
-        <v>10.4764547348022</v>
+        <v>10.4764537811279</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>10.2371435165405</v>
+        <v>10.2371444702148</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G513" t="n">
-        <v>10.3235607147217</v>
+        <v>10.3235626220703</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G514" t="n">
-        <v>10.3966836929321</v>
+        <v>10.3966846466064</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G516" t="n">
-        <v>10.5961084365845</v>
+        <v>10.5961074829102</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G517" t="n">
-        <v>10.70911693573</v>
+        <v>10.7091159820557</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>10.6027555465698</v>
+        <v>10.6027574539185</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G520" t="n">
-        <v>10.6160507202148</v>
+        <v>10.6160516738892</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G521" t="n">
-        <v>10.6825265884399</v>
+        <v>10.6825246810913</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G522" t="n">
-        <v>10.9617195129395</v>
+        <v>10.9617214202881</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>11.0016050338745</v>
+        <v>11.0016059875488</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G526" t="n">
-        <v>11.2209730148315</v>
+        <v>11.2209711074829</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>11.2675046920776</v>
+        <v>11.267505645752</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G530" t="n">
-        <v>11.2143259048462</v>
+        <v>11.2143268585205</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G533" t="n">
-        <v>11.0813770294189</v>
+        <v>11.0813760757446</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G534" t="n">
-        <v>11.1810874938965</v>
+        <v>11.1810884475708</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>10.8952465057373</v>
+        <v>10.895245552063</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G536" t="n">
-        <v>10.6825265884399</v>
+        <v>10.6825246810913</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>10.4033298492432</v>
+        <v>10.4033308029175</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G538" t="n">
-        <v>10.6758794784546</v>
+        <v>10.675877571106</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>10.4033298492432</v>
+        <v>10.4033308029175</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G540" t="n">
-        <v>10.4299221038818</v>
+        <v>10.4299201965332</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G541" t="n">
-        <v>10.516339302063</v>
+        <v>10.5163383483887</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G543" t="n">
-        <v>10.4764547348022</v>
+        <v>10.4764537811279</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G545" t="n">
-        <v>10.7490005493164</v>
+        <v>10.7490015029907</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>11.1013193130493</v>
+        <v>11.101318359375</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G551" t="n">
-        <v>11.2475643157959</v>
+        <v>11.2475633621216</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>11.1212596893311</v>
+        <v>11.1212606430054</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>16.75</v>
       </c>
       <c r="G554" t="n">
-        <v>11.1345558166504</v>
+        <v>11.1345548629761</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G556" t="n">
-        <v>11.3273324966431</v>
+        <v>11.3273334503174</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G558" t="n">
-        <v>11.4071044921875</v>
+        <v>11.4071025848389</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G559" t="n">
-        <v>12.1250314712524</v>
+        <v>12.1250324249268</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G561" t="n">
-        <v>12.8097267150879</v>
+        <v>12.8097248077393</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G562" t="n">
-        <v>12.7498970031738</v>
+        <v>12.7498998641968</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.25</v>
       </c>
       <c r="G563" t="n">
-        <v>12.7964296340942</v>
+        <v>12.7964305877686</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>12.9958534240723</v>
+        <v>12.9958543777466</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G565" t="n">
-        <v>12.9426755905151</v>
+        <v>12.9426746368408</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G566" t="n">
-        <v>12.6701278686523</v>
+        <v>12.6701259613037</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G567" t="n">
-        <v>12.6036510467529</v>
+        <v>12.6036520004272</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G568" t="n">
-        <v>12.6036510467529</v>
+        <v>12.6036520004272</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G569" t="n">
-        <v>12.4906463623047</v>
+        <v>12.490647315979</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G571" t="n">
-        <v>12.450758934021</v>
+        <v>12.4507608413696</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7831363677979</v>
+        <v>12.7831354141235</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G573" t="n">
-        <v>12.9426755905151</v>
+        <v>12.9426746368408</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G574" t="n">
-        <v>12.8828468322754</v>
+        <v>12.8828477859497</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.75</v>
       </c>
       <c r="G575" t="n">
-        <v>13.1288061141968</v>
+        <v>13.1288032531738</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G576" t="n">
-        <v>13.2019271850586</v>
+        <v>13.2019300460815</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>13.0955667495728</v>
+        <v>13.0955677032471</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G578" t="n">
-        <v>13.3215808868408</v>
+        <v>13.3215827941895</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>19.75</v>
       </c>
       <c r="G579" t="n">
-        <v>13.1288061141968</v>
+        <v>13.1288032531738</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G580" t="n">
-        <v>13.3348789215088</v>
+        <v>13.3348770141602</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G581" t="n">
-        <v>12.4906463623047</v>
+        <v>12.490647315979</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G582" t="n">
-        <v>12.6235971450806</v>
+        <v>12.6235961914062</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>12.4906463623047</v>
+        <v>12.490647315979</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G585" t="n">
-        <v>12.8030786514282</v>
+        <v>12.8030757904053</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G586" t="n">
-        <v>12.8429613113403</v>
+        <v>12.8429622650146</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>12.8961420059204</v>
+        <v>12.8961410522461</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G589" t="n">
-        <v>12.8828468322754</v>
+        <v>12.8828477859497</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>13.0290937423706</v>
+        <v>13.0290927886963</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G591" t="n">
-        <v>13.0290937423706</v>
+        <v>13.0290927886963</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G592" t="n">
-        <v>13.1487483978271</v>
+        <v>13.1487493515015</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.228515625</v>
+        <v>13.2285165786743</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>20</v>
       </c>
       <c r="G595" t="n">
-        <v>13.2949924468994</v>
+        <v>13.2949905395508</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>13.2617559432983</v>
+        <v>13.2617568969727</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G597" t="n">
-        <v>13.3082895278931</v>
+        <v>13.3082866668701</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G599" t="n">
-        <v>13.3348789215088</v>
+        <v>13.3348770141602</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>13.228515625</v>
+        <v>13.2285165786743</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G606" t="n">
-        <v>12.5504713058472</v>
+        <v>12.5504732131958</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G608" t="n">
-        <v>13.4204368591309</v>
+        <v>13.4204359054565</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G610" t="n">
-        <v>13.217755317688</v>
+        <v>13.2177534103394</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G613" t="n">
-        <v>12.6893358230591</v>
+        <v>12.6893348693848</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G614" t="n">
-        <v>12.566276550293</v>
+        <v>12.5662775039673</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>12.9209718704224</v>
+        <v>12.920970916748</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G618" t="n">
-        <v>12.892014503479</v>
+        <v>12.8920164108276</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>12.9933576583862</v>
+        <v>12.9933557510376</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G621" t="n">
-        <v>13.1598472595215</v>
+        <v>13.1598463058472</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G623" t="n">
-        <v>13.8692331314087</v>
+        <v>13.8692302703857</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>14.0429573059082</v>
+        <v>14.0429582595825</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G626" t="n">
-        <v>14.0863904953003</v>
+        <v>14.086389541626</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G627" t="n">
-        <v>13.7606525421143</v>
+        <v>13.7606544494629</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>19.75</v>
       </c>
       <c r="G630" t="n">
-        <v>14.296311378479</v>
+        <v>14.2963104248047</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>19.5</v>
       </c>
       <c r="G631" t="n">
-        <v>14.1153450012207</v>
+        <v>14.115345954895</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G632" t="n">
-        <v>14.1949739456177</v>
+        <v>14.194972038269</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>13.4638681411743</v>
+        <v>13.4638700485229</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G638" t="n">
-        <v>13.4421520233154</v>
+        <v>13.4421529769897</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>13.5652084350586</v>
+        <v>13.5652093887329</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G642" t="n">
-        <v>13.9995288848877</v>
+        <v>13.9995279312134</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G643" t="n">
-        <v>14.1225843429565</v>
+        <v>14.1225824356079</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G645" t="n">
-        <v>14.1587791442871</v>
+        <v>14.1587762832642</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G646" t="n">
-        <v>14.2094459533691</v>
+        <v>14.2094469070435</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G647" t="n">
-        <v>14.1587791442871</v>
+        <v>14.1587762832642</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G648" t="n">
-        <v>14.2383995056152</v>
+        <v>14.2384052276611</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G649" t="n">
-        <v>14.2022085189819</v>
+        <v>14.2022094726562</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>14.0429573059082</v>
+        <v>14.0429582595825</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>13.9850492477417</v>
+        <v>13.985050201416</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G657" t="n">
-        <v>13.9488592147827</v>
+        <v>13.9488573074341</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G661" t="n">
-        <v>13.4059610366821</v>
+        <v>13.4059600830078</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G662" t="n">
-        <v>13.3263359069824</v>
+        <v>13.3263330459595</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G663" t="n">
-        <v>13.3190937042236</v>
+        <v>13.3190956115723</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G665" t="n">
-        <v>13.6593132019043</v>
+        <v>13.65931224823</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G666" t="n">
-        <v>13.7823696136475</v>
+        <v>13.7823686599731</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>18.5</v>
       </c>
       <c r="G669" t="n">
-        <v>13.3914813995361</v>
+        <v>13.3914823532104</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G670" t="n">
-        <v>13.0802211761475</v>
+        <v>13.0802192687988</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G674" t="n">
-        <v>13.0440282821655</v>
+        <v>13.0440273284912</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G675" t="n">
-        <v>12.942684173584</v>
+        <v>12.9426851272583</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>12.9933576583862</v>
+        <v>12.9933557510376</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>13.0657415390015</v>
+        <v>13.0657434463501</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G680" t="n">
-        <v>12.892014503479</v>
+        <v>12.8920164108276</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G681" t="n">
-        <v>12.9137334823608</v>
+        <v>12.9137325286865</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G683" t="n">
-        <v>12.9282093048096</v>
+        <v>12.9282102584839</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>12.7761974334717</v>
+        <v>12.7761964797974</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G686" t="n">
-        <v>12.9064931869507</v>
+        <v>12.9064922332764</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>13.3190937042236</v>
+        <v>13.3190956115723</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G688" t="n">
-        <v>13.2394714355469</v>
+        <v>13.2394723892212</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G689" t="n">
-        <v>13.0512676239014</v>
+        <v>13.0512666702271</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G690" t="n">
-        <v>12.9861183166504</v>
+        <v>12.9861192703247</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G691" t="n">
-        <v>12.942684173584</v>
+        <v>12.9426851272583</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G692" t="n">
-        <v>12.9644031524658</v>
+        <v>12.9644021987915</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G693" t="n">
-        <v>12.9644031524658</v>
+        <v>12.9644021987915</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>12.6314258575439</v>
+        <v>12.6314268112183</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G697" t="n">
-        <v>12.7689580917358</v>
+        <v>12.7689590454102</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G698" t="n">
-        <v>12.7834377288818</v>
+        <v>12.7834367752075</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G699" t="n">
-        <v>12.9282093048096</v>
+        <v>12.9282102584839</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G702" t="n">
-        <v>12.8775386810303</v>
+        <v>12.8775396347046</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G703" t="n">
-        <v>12.892014503479</v>
+        <v>12.8920164108276</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G704" t="n">
-        <v>12.8775386810303</v>
+        <v>12.8775396347046</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G705" t="n">
-        <v>12.76171875</v>
+        <v>12.7617197036743</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>12.6314258575439</v>
+        <v>12.6314268112183</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>12.3780727386475</v>
+        <v>12.3780736923218</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G708" t="n">
-        <v>12.4649362564087</v>
+        <v>12.4649353027344</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>12.0161409378052</v>
+        <v>12.0161418914795</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>12.1971063613892</v>
+        <v>12.1971073150635</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G712" t="n">
-        <v>12.1102409362793</v>
+        <v>12.1102428436279</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G717" t="n">
-        <v>12.4070272445679</v>
+        <v>12.4070262908936</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G718" t="n">
-        <v>12.0306177139282</v>
+        <v>12.0306196212769</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G719" t="n">
-        <v>11.9075603485107</v>
+        <v>11.9075613021851</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>11.9582319259644</v>
+        <v>11.95823097229</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G723" t="n">
-        <v>11.9365148544312</v>
+        <v>11.9365167617798</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G724" t="n">
-        <v>11.9365148544312</v>
+        <v>11.9365167617798</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>11.6180152893066</v>
+        <v>11.6180143356323</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>11.6180152893066</v>
+        <v>11.6180143356323</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>12.0885286331177</v>
+        <v>12.0885276794434</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G730" t="n">
-        <v>11.9582319259644</v>
+        <v>11.95823097229</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G731" t="n">
-        <v>12.1030035018921</v>
+        <v>12.1030044555664</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G732" t="n">
-        <v>12.2767305374146</v>
+        <v>12.2767314910889</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G734" t="n">
-        <v>12.2984485626221</v>
+        <v>12.2984466552734</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G735" t="n">
-        <v>12.2115831375122</v>
+        <v>12.2115840911865</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>12.269492149353</v>
+        <v>12.2694931030273</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>12.2332992553711</v>
+        <v>12.2333002090454</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G738" t="n">
-        <v>11.9147996902466</v>
+        <v>11.9147977828979</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>11.8930835723877</v>
+        <v>11.893084526062</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G742" t="n">
-        <v>11.8858451843262</v>
+        <v>11.8858461380005</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>11.6180152893066</v>
+        <v>11.6180143356323</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G747" t="n">
-        <v>11.7265949249268</v>
+        <v>11.7265958786011</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G750" t="n">
-        <v>11.5311517715454</v>
+        <v>11.5311527252197</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>16</v>
       </c>
       <c r="G751" t="n">
-        <v>11.5818223953247</v>
+        <v>11.581823348999</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G753" t="n">
-        <v>11.371901512146</v>
+        <v>11.3719024658203</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>16</v>
       </c>
       <c r="G754" t="n">
-        <v>11.5818223953247</v>
+        <v>11.581823348999</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G755" t="n">
-        <v>12.0016622543335</v>
+        <v>12.0016632080078</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G757" t="n">
-        <v>11.7410726547241</v>
+        <v>11.7410717010498</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G758" t="n">
-        <v>12.2477769851685</v>
+        <v>12.2477779388428</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G759" t="n">
-        <v>12.7255277633667</v>
+        <v>12.7255268096924</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G760" t="n">
-        <v>12.5518016815186</v>
+        <v>12.5517997741699</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G764" t="n">
-        <v>11.9147996902466</v>
+        <v>11.9147977828979</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G765" t="n">
-        <v>12.0378561019897</v>
+        <v>12.0378551483154</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>12.269492149353</v>
+        <v>12.2694931030273</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G768" t="n">
-        <v>12.4576959609985</v>
+        <v>12.4576969146729</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G770" t="n">
-        <v>12.2839708328247</v>
+        <v>12.2839689254761</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="n">
-        <v>12.6169481277466</v>
+        <v>12.6169462203979</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="n">
-        <v>12.5373220443726</v>
+        <v>12.5373229980469</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="n">
-        <v>12.6531400680542</v>
+        <v>12.6531391143799</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="n">
-        <v>12.3491182327271</v>
+        <v>12.3491172790527</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>12.3780727386475</v>
+        <v>12.3780736923218</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>12.269492149353</v>
+        <v>12.2694931030273</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="n">
-        <v>12.2188234329224</v>
+        <v>12.2188205718994</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="n">
-        <v>12.6459007263184</v>
+        <v>12.6459016799927</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="n">
-        <v>12.6676168441772</v>
+        <v>12.6676187515259</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>12.4576959609985</v>
+        <v>12.4576969146729</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>12.4576959609985</v>
+        <v>12.4576969146729</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>12.3780727386475</v>
+        <v>12.3780736923218</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="n">
-        <v>12.6241855621338</v>
+        <v>12.6241865158081</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>12.5735168457031</v>
+        <v>12.5735149383545</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>12.4142665863037</v>
+        <v>12.4142646789551</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>12.5518016815186</v>
+        <v>12.5517997741699</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="n">
-        <v>12.5445613861084</v>
+        <v>12.5445623397827</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="n">
-        <v>12.7327651977539</v>
+        <v>12.7327680587769</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="n">
-        <v>12.7327651977539</v>
+        <v>12.7327680587769</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="n">
-        <v>12.3346405029297</v>
+        <v>12.3346424102783</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="n">
-        <v>12.1464347839355</v>
+        <v>12.1464366912842</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="n">
-        <v>12.15367603302</v>
+        <v>12.1536750793457</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G815" t="n">
-        <v>12.1102409362793</v>
+        <v>12.1102428436279</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="n">
-        <v>12.1247205734253</v>
+        <v>12.124719619751</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>11.9799461364746</v>
+        <v>11.9799480438232</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G818" t="n">
-        <v>11.9582319259644</v>
+        <v>11.95823097229</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>12.2477769851685</v>
+        <v>12.2477779388428</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>12.269492149353</v>
+        <v>12.2694931030273</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>12.2332992553711</v>
+        <v>12.2333002090454</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G826" t="n">
-        <v>12.2115831375122</v>
+        <v>12.2115840911865</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>12.2332992553711</v>
+        <v>12.2333002090454</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G828" t="n">
-        <v>12.1030035018921</v>
+        <v>12.1030044555664</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G830" t="n">
-        <v>12.0016622543335</v>
+        <v>12.0016632080078</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>12.0885286331177</v>
+        <v>12.0885276794434</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G834" t="n">
-        <v>12.2477769851685</v>
+        <v>12.2477779388428</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G836" t="n">
-        <v>12.0885286331177</v>
+        <v>12.0885276794434</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G838" t="n">
-        <v>12.0378561019897</v>
+        <v>12.0378551483154</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G840" t="n">
-        <v>11.9147996902466</v>
+        <v>11.9147977828979</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="n">
-        <v>11.7917432785034</v>
+        <v>11.7917442321777</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>11.7410726547241</v>
+        <v>11.7410717010498</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="n">
-        <v>11.6686868667603</v>
+        <v>11.6686859130859</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>11.6542081832886</v>
+        <v>11.6542091369629</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>11.9075603485107</v>
+        <v>11.9075613021851</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>11.9799461364746</v>
+        <v>11.9799480438232</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G848" t="n">
-        <v>11.9147996902466</v>
+        <v>11.9147977828979</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="n">
-        <v>11.7483100891113</v>
+        <v>11.7483110427856</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="n">
-        <v>11.6397304534912</v>
+        <v>11.6397323608398</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="n">
-        <v>11.7555494308472</v>
+        <v>11.7555484771729</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="n">
-        <v>12.3346405029297</v>
+        <v>12.3346424102783</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>12.7218399047852</v>
+        <v>12.7218408584595</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="n">
-        <v>12.873291015625</v>
+        <v>12.8732929229736</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="n">
-        <v>13.2670640945435</v>
+        <v>13.2670612335205</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="n">
-        <v>13.1610479354858</v>
+        <v>13.1610450744629</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="n">
-        <v>13.1459016799927</v>
+        <v>13.1459035873413</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="n">
-        <v>13.1307582855225</v>
+        <v>13.1307563781738</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="n">
-        <v>13.1610479354858</v>
+        <v>13.1610450744629</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>13.0777502059937</v>
+        <v>13.0777492523193</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="n">
-        <v>12.9944515228271</v>
+        <v>12.9944505691528</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="n">
-        <v>13.5396709442139</v>
+        <v>13.5396728515625</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="n">
-        <v>13.6305437088013</v>
+        <v>13.6305456161499</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8501482009888</v>
+        <v>13.8501491546631</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>13.9713096618652</v>
+        <v>13.9713068008423</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="n">
-        <v>14.0924673080444</v>
+        <v>14.0924692153931</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>14.0470323562622</v>
+        <v>14.0470304489136</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5548181533813</v>
+        <v>13.55482006073</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4336566925049</v>
+        <v>13.4336585998535</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="n">
-        <v>13.6305437088013</v>
+        <v>13.6305456161499</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="n">
-        <v>13.6305437088013</v>
+        <v>13.6305456161499</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="n">
-        <v>14.0697507858276</v>
+        <v>14.0697498321533</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="n">
-        <v>13.9864501953125</v>
+        <v>13.9864511489868</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="n">
-        <v>13.7971391677856</v>
+        <v>13.797137260437</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>14.4635229110718</v>
+        <v>14.4635219573975</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>14.3499345779419</v>
+        <v>14.3499317169189</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>14.274209022522</v>
+        <v>14.2742080688477</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="n">
-        <v>14.0167427062988</v>
+        <v>14.0167446136475</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="n">
-        <v>13.6078252792358</v>
+        <v>13.6078233718872</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="n">
-        <v>13.6381149291992</v>
+        <v>13.6381168365479</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="n">
-        <v>13.4563760757446</v>
+        <v>13.4563751220703</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="n">
-        <v>13.2670640945435</v>
+        <v>13.2670612335205</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="n">
-        <v>13.27463722229</v>
+        <v>13.2746362686157</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="n">
-        <v>13.27463722229</v>
+        <v>13.2746362686157</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="n">
-        <v>13.6078252792358</v>
+        <v>13.6078233718872</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>13.5926818847656</v>
+        <v>13.5926809310913</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="n">
-        <v>13.6835527420044</v>
+        <v>13.6835508346558</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="n">
-        <v>13.6002531051636</v>
+        <v>13.6002511978149</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0474586486816</v>
+        <v>13.047459602356</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>12.9868803024292</v>
+        <v>12.9868783950806</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="n">
-        <v>13.0853204727173</v>
+        <v>13.0853214263916</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="n">
-        <v>12.941442489624</v>
+        <v>12.9414434432983</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>12.7975654602051</v>
+        <v>12.7975664138794</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="n">
-        <v>13.2291994094849</v>
+        <v>13.2291984558105</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="n">
-        <v>13.3124990463257</v>
+        <v>13.3124971389771</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="n">
-        <v>13.2519159317017</v>
+        <v>13.2519178390503</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="n">
-        <v>13.1989107131958</v>
+        <v>13.1989088058472</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="n">
-        <v>13.2064819335938</v>
+        <v>13.2064838409424</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="n">
-        <v>13.51695728302</v>
+        <v>13.5169563293457</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="n">
-        <v>13.3352165222168</v>
+        <v>13.3352155685425</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="n">
-        <v>13.4866647720337</v>
+        <v>13.4866666793823</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="n">
-        <v>13.865291595459</v>
+        <v>13.8652906417847</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="n">
-        <v>14.0318880081177</v>
+        <v>14.031888961792</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="n">
-        <v>13.653263092041</v>
+        <v>13.6532621383667</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>13.5093851089478</v>
+        <v>13.5093841552734</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="n">
-        <v>13.6305437088013</v>
+        <v>13.6305456161499</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="n">
-        <v>13.6835527420044</v>
+        <v>13.6835508346558</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>14.3347883224487</v>
+        <v>14.3347873687744</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="n">
-        <v>14.2211999893188</v>
+        <v>14.2212028503418</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="n">
-        <v>14.3575057983398</v>
+        <v>14.3575038909912</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="n">
-        <v>14.1984844207764</v>
+        <v>14.1984825134277</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="n">
-        <v>14.1151847839355</v>
+        <v>14.1151838302612</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="n">
-        <v>14.3802251815796</v>
+        <v>14.380223274231</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="n">
-        <v>14.1530485153198</v>
+        <v>14.1530494689941</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="n">
-        <v>14.0621776580811</v>
+        <v>14.0621767044067</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="n">
-        <v>14.0091705322266</v>
+        <v>14.0091695785522</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="n">
-        <v>13.9182987213135</v>
+        <v>13.9183015823364</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="n">
-        <v>13.6078252792358</v>
+        <v>13.6078233718872</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="n">
-        <v>13.5472459793091</v>
+        <v>13.5472478866577</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="n">
-        <v>13.8501482009888</v>
+        <v>13.8501491546631</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.895583152771</v>
+        <v>13.8955812454224</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.8122844696045</v>
+        <v>13.8122863769531</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="n">
-        <v>13.585108757019</v>
+        <v>13.5851097106934</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="n">
-        <v>13.653263092041</v>
+        <v>13.6532621383667</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="n">
-        <v>13.7744216918945</v>
+        <v>13.7744226455688</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="n">
-        <v>14.0167427062988</v>
+        <v>14.0167446136475</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>13.7441301345825</v>
+        <v>13.7441329956055</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>13.9713096618652</v>
+        <v>13.9713068008423</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="n">
-        <v>14.0167427062988</v>
+        <v>14.0167446136475</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="n">
-        <v>14.3650770187378</v>
+        <v>14.3650779724121</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.3120708465576</v>
+        <v>14.3120698928833</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="n">
-        <v>14.3120708465576</v>
+        <v>14.3120698928833</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="n">
-        <v>13.9107275009155</v>
+        <v>13.9107265472412</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="n">
-        <v>13.9107275009155</v>
+        <v>13.9107265472412</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="n">
-        <v>13.75927734375</v>
+        <v>13.7592763900757</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7668504714966</v>
+        <v>13.7668485641479</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="n">
-        <v>14.0243167877197</v>
+        <v>14.0243158340454</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="n">
-        <v>14.1984844207764</v>
+        <v>14.1984825134277</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="n">
-        <v>14.440803527832</v>
+        <v>14.4408016204834</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.3650770187378</v>
+        <v>14.3650779724121</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="n">
-        <v>14.2211999893188</v>
+        <v>14.2212028503418</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="n">
-        <v>13.9940252304077</v>
+        <v>13.994026184082</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="n">
-        <v>13.9107275009155</v>
+        <v>13.9107265472412</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="n">
-        <v>13.895583152771</v>
+        <v>13.8955812454224</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="n">
-        <v>14.4105157852173</v>
+        <v>14.4105129241943</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.827000617981</v>
+        <v>14.8270053863525</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="n">
-        <v>15.1904850006104</v>
+        <v>15.1904830932617</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>15.0466089248657</v>
+        <v>15.0466070175171</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.6528339385986</v>
+        <v>14.6528358459473</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>14.69069480896</v>
+        <v>14.6906967163086</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="n">
-        <v>14.9405908584595</v>
+        <v>14.9405918121338</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="n">
-        <v>14.3802251815796</v>
+        <v>14.380223274231</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="n">
-        <v>14.5771102905273</v>
+        <v>14.577109336853</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.508957862854</v>
+        <v>14.5089550018311</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>14.5392475128174</v>
+        <v>14.5392456054688</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.4938125610352</v>
+        <v>14.4938106536865</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.5392475128174</v>
+        <v>14.5392456054688</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.6528339385986</v>
+        <v>14.6528358459473</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.6301164627075</v>
+        <v>14.6301183700562</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6604061126709</v>
+        <v>14.6604080200195</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.9481630325317</v>
+        <v>14.9481620788574</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.781569480896</v>
+        <v>14.7815685272217</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.5846815109253</v>
+        <v>14.5846824645996</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.6301164627075</v>
+        <v>14.6301183700562</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.516529083252</v>
+        <v>14.5165300369263</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="n">
-        <v>14.6604061126709</v>
+        <v>14.6604080200195</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>14.7437057495117</v>
+        <v>14.743706703186</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.827000617981</v>
+        <v>14.8270053863525</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.0996112823486</v>
+        <v>15.0996131896973</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.599401473999</v>
+        <v>15.5993995666504</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.8568649291992</v>
+        <v>15.8568658828735</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>16.3112182617188</v>
+        <v>16.3112163543701</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.2052021026611</v>
+        <v>16.2052001953125</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.356653213501</v>
+        <v>16.3566551208496</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.3263607025146</v>
+        <v>16.3263645172119</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.9780282974243</v>
+        <v>15.97802734375</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="n">
-        <v>16.1749134063721</v>
+        <v>16.1749114990234</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="n">
-        <v>16.4626693725586</v>
+        <v>16.46266746521</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="n">
-        <v>16.1597671508789</v>
+        <v>16.1597652435303</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="n">
-        <v>16.492956161499</v>
+        <v>16.4929618835449</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="n">
-        <v>16.492956161499</v>
+        <v>16.4929618835449</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="n">
-        <v>16.6141204833984</v>
+        <v>16.6141185760498</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="n">
-        <v>16.8564414978027</v>
+        <v>16.8564395904541</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="n">
-        <v>16.6595516204834</v>
+        <v>16.659553527832</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.1139068603516</v>
+        <v>17.1139030456543</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.4016609191895</v>
+        <v>17.4016590118408</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.3562259674072</v>
+        <v>17.3562240600586</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.5834007263184</v>
+        <v>17.5833988189697</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.4319534301758</v>
+        <v>17.4319515228271</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="n">
-        <v>16.6292610168457</v>
+        <v>16.629264831543</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>16.7352771759033</v>
+        <v>16.7352809906006</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>15.9780282974243</v>
+        <v>15.97802734375</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="n">
-        <v>15.7962846755981</v>
+        <v>15.7962865829468</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="n">
-        <v>16.3263607025146</v>
+        <v>16.3263645172119</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="n">
-        <v>16.7504253387451</v>
+        <v>16.7504234313965</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="n">
-        <v>16.4172344207764</v>
+        <v>16.417236328125</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="n">
-        <v>15.7962846755981</v>
+        <v>15.7962865829468</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>14.3499345779419</v>
+        <v>14.3499317169189</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="n">
-        <v>13.2291994094849</v>
+        <v>13.2291984558105</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="n">
-        <v>10.6924047470093</v>
+        <v>10.692403793335</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="n">
-        <v>11.3209228515625</v>
+        <v>11.3209238052368</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.1240367889404</v>
+        <v>11.1240386962891</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.131609916687</v>
+        <v>11.1316108703613</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="n">
-        <v>10.8741445541382</v>
+        <v>10.8741455078125</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="n">
-        <v>11.5102367401123</v>
+        <v>11.510235786438</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>11.6541137695312</v>
+        <v>11.6541147232056</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>12.1539011001587</v>
+        <v>12.1539001464844</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.6536865234375</v>
+        <v>12.6536874771118</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.8960103988647</v>
+        <v>12.8960094451904</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.6688318252563</v>
+        <v>12.6688327789307</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1085" t="n">
-        <v>12.5628175735474</v>
+        <v>12.5628185272217</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.8808641433716</v>
+        <v>12.8808650970459</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.5401000976562</v>
+        <v>12.5401010513306</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.5325269699097</v>
+        <v>12.532527923584</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.7899932861328</v>
+        <v>12.7899923324585</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.7975654602051</v>
+        <v>12.7975664138794</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.8581457138062</v>
+        <v>12.8581447601318</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.9262990951538</v>
+        <v>12.9262981414795</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="n">
-        <v>13.3124990463257</v>
+        <v>13.3124971389771</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3810777664185</v>
+        <v>12.3810758590698</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.4795207977295</v>
+        <v>12.4795198440552</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.6158266067505</v>
+        <v>12.6158256530762</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.873291015625</v>
+        <v>12.8732929229736</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.6461172103882</v>
+        <v>12.6461162567139</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1107" t="n">
-        <v>13.0398874282837</v>
+        <v>13.0398864746094</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1109" t="n">
-        <v>13.1231851577759</v>
+        <v>13.1231832504272</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1114" t="n">
-        <v>13.6772384643555</v>
+        <v>13.6772394180298</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1116" t="n">
-        <v>14.5953874588013</v>
+        <v>14.5953884124756</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>18.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>14.6428785324097</v>
+        <v>14.6428775787354</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>19.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>15.4343843460083</v>
+        <v>15.4343862533569</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1120" t="n">
-        <v>15.7984790802002</v>
+        <v>15.7984771728516</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1121" t="n">
-        <v>15.4502172470093</v>
+        <v>15.4502153396606</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1122" t="n">
-        <v>15.4027242660522</v>
+        <v>15.4027252197266</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>19.5</v>
       </c>
       <c r="G1124" t="n">
-        <v>15.4343843460083</v>
+        <v>15.4343862533569</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>19.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>15.4343843460083</v>
+        <v>15.4343862533569</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>14.9199066162109</v>
+        <v>14.9199056625366</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1127" t="n">
-        <v>14.8644990921021</v>
+        <v>14.864501953125</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>14.5637254714966</v>
+        <v>14.5637273788452</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1130" t="n">
-        <v>14.6270484924316</v>
+        <v>14.627046585083</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>15.1573572158813</v>
+        <v>15.1573581695557</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1132" t="n">
-        <v>14.9832258224487</v>
+        <v>14.9832248687744</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>14.9990568161011</v>
+        <v>14.9990577697754</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1134" t="n">
-        <v>14.9119901657104</v>
+        <v>14.9119911193848</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>15.1177835464478</v>
+        <v>15.1177825927734</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1136" t="n">
-        <v>15.1811037063599</v>
+        <v>15.1811046600342</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1138" t="n">
-        <v>14.7695188522339</v>
+        <v>14.7695169448853</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1139" t="n">
-        <v>14.8961601257324</v>
+        <v>14.8961591720581</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1140" t="n">
-        <v>15.1811037063599</v>
+        <v>15.1811046600342</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G1141" t="n">
-        <v>15.1890172958374</v>
+        <v>15.1890163421631</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>19.75</v>
       </c>
       <c r="G1142" t="n">
-        <v>15.6322612762451</v>
+        <v>15.6322631835938</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1148" t="n">
-        <v>16.5899868011475</v>
+        <v>16.5899848937988</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>21.5</v>
       </c>
       <c r="G1150" t="n">
-        <v>17.0174007415771</v>
+        <v>17.0173988342285</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1154" t="n">
-        <v>16.5741539001465</v>
+        <v>16.5741558074951</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G1159" t="n">
-        <v>16.2575531005859</v>
+        <v>16.2575511932373</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1160" t="n">
-        <v>16.099250793457</v>
+        <v>16.0992527008057</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G1162" t="n">
-        <v>16.1309089660645</v>
+        <v>16.1309108734131</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1164" t="n">
-        <v>16.289213180542</v>
+        <v>16.2892112731934</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G1166" t="n">
-        <v>16.8432655334473</v>
+        <v>16.8432674407959</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1167" t="n">
-        <v>16.7324562072754</v>
+        <v>16.7324542999268</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>17.1598720550537</v>
+        <v>17.1598701477051</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1174" t="n">
-        <v>17.6822662353516</v>
+        <v>17.6822643280029</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1175" t="n">
-        <v>17.3814888000488</v>
+        <v>17.3814907073975</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1182" t="n">
-        <v>17.6822662353516</v>
+        <v>17.6822643280029</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>22</v>
       </c>
       <c r="G1188" t="n">
-        <v>17.4131507873535</v>
+        <v>17.4131526947021</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>21.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>17.0174007415771</v>
+        <v>17.0173988342285</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G1190" t="n">
-        <v>17.2865123748779</v>
+        <v>17.2865104675293</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1193" t="n">
-        <v>17.3814888000488</v>
+        <v>17.3814907073975</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>21.5</v>
       </c>
       <c r="G1195" t="n">
-        <v>17.0174007415771</v>
+        <v>17.0173988342285</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1196" t="n">
-        <v>16.9065895080566</v>
+        <v>16.906587600708</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G1198" t="n">
-        <v>16.9540767669678</v>
+        <v>16.9540786743164</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1202" t="n">
-        <v>16.6058158874512</v>
+        <v>16.6058139801025</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1204" t="n">
-        <v>16.6058158874512</v>
+        <v>16.6058139801025</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1205" t="n">
-        <v>16.6533050537109</v>
+        <v>16.6533069610596</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1208" t="n">
-        <v>17.3814888000488</v>
+        <v>17.3814907073975</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1213" t="n">
-        <v>17.8563976287842</v>
+        <v>17.8563957214355</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1216" t="n">
-        <v>17.3656635284424</v>
+        <v>17.3656616210938</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1219" t="n">
-        <v>17.3814888000488</v>
+        <v>17.3814907073975</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>17.1757011413574</v>
+        <v>17.1756992340088</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1225" t="n">
-        <v>15.9251184463501</v>
+        <v>15.9251203536987</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>15.5926876068115</v>
+        <v>15.5926856994629</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1227" t="n">
-        <v>15.2681703567505</v>
+        <v>15.2681694030762</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>15.3552322387695</v>
+        <v>15.3552360534668</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1229" t="n">
-        <v>15.4027242660522</v>
+        <v>15.4027252197266</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1231" t="n">
-        <v>15.7984790802002</v>
+        <v>15.7984771728516</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1232" t="n">
-        <v>16.3525314331055</v>
+        <v>16.3525333404541</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1234" t="n">
-        <v>16.6533050537109</v>
+        <v>16.6533069610596</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1235" t="n">
-        <v>16.3367042541504</v>
+        <v>16.3367023468018</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G1237" t="n">
-        <v>16.1309089660645</v>
+        <v>16.1309108734131</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G1243" t="n">
-        <v>16.2733821868896</v>
+        <v>16.2733840942383</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1244" t="n">
-        <v>16.3367042541504</v>
+        <v>16.3367023468018</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.3525314331055</v>
+        <v>16.3525333404541</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.9092903137207</v>
+        <v>15.9092884063721</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.7747316360474</v>
+        <v>15.774733543396</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G1254" t="n">
-        <v>16.2733821868896</v>
+        <v>16.2733840942383</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>16.3050441741943</v>
+        <v>16.305046081543</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.3367042541504</v>
+        <v>16.3367023468018</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G1263" t="n">
-        <v>16.7957782745361</v>
+        <v>16.7957763671875</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G1275" t="n">
-        <v>19.8193340301514</v>
+        <v>19.8193321228027</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>25</v>
       </c>
       <c r="G1276" t="n">
-        <v>19.7876758575439</v>
+        <v>19.7876739501953</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>25</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.7876758575439</v>
+        <v>19.7876739501953</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G1280" t="n">
-        <v>20.0409564971924</v>
+        <v>20.0409545898438</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>21.054084777832</v>
+        <v>21.0540828704834</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1291" t="n">
-        <v>20.0092964172363</v>
+        <v>20.0092945098877</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1293" t="n">
-        <v>20.3892211914062</v>
+        <v>20.3892192840576</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6741600036621</v>
+        <v>20.6741619110107</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.5000305175781</v>
+        <v>20.5000286102295</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1303" t="n">
-        <v>19.8509922027588</v>
+        <v>19.8509941101074</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.3417282104492</v>
+        <v>20.3417301177979</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1306" t="n">
-        <v>19.8984870910645</v>
+        <v>19.8984851837158</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1307" t="n">
-        <v>19.8984870910645</v>
+        <v>19.8984851837158</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.774543762207</v>
+        <v>18.7745456695557</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.3285999298096</v>
+        <v>19.3285980224609</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G1314" t="n">
-        <v>18.5054321289062</v>
+        <v>18.5054302215576</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>18.125509262085</v>
+        <v>18.1255073547363</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1318" t="n">
-        <v>20.2942352294922</v>
+        <v>20.2942371368408</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>20.5000305175781</v>
+        <v>20.5000286102295</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>25.9599990844727</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.5475177764893</v>
+        <v>20.5475196838379</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.1544666290283</v>
+        <v>19.154468536377</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.4710731506348</v>
+        <v>19.4710712432861</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1328" t="n">
-        <v>19.6768627166748</v>
+        <v>19.6768608093262</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.7560138702393</v>
+        <v>19.7560119628906</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1359367370605</v>
+        <v>20.1359348297119</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>25.5</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.1834278106689</v>
+        <v>20.1834259033203</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.1201057434082</v>
+        <v>20.1201076507568</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G1337" t="n">
-        <v>20.1992588043213</v>
+        <v>20.1992607116699</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1338" t="n">
-        <v>19.8984870910645</v>
+        <v>19.8984851837158</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.8509922027588</v>
+        <v>19.8509941101074</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.8509922027588</v>
+        <v>19.8509941101074</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G1344" t="n">
-        <v>19.7243518829346</v>
+        <v>19.7243537902832</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G1347" t="n">
-        <v>20.2467479705811</v>
+        <v>20.2467460632324</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1350" t="n">
-        <v>20.3417282104492</v>
+        <v>20.3417301177979</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1353" t="n">
-        <v>19.6768627166748</v>
+        <v>19.6768608093262</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.2177886962891</v>
+        <v>19.2177867889404</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1362" t="n">
-        <v>19.4235782623291</v>
+        <v>19.4235801696777</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>18.9170150756836</v>
+        <v>18.917013168335</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G1369" t="n">
-        <v>20.4353523254395</v>
+        <v>20.4353504180908</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1370" t="n">
-        <v>20.4190292358398</v>
+        <v>20.4190311431885</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.1741962432861</v>
+        <v>20.1741943359375</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G1373" t="n">
-        <v>20.4353523254395</v>
+        <v>20.4353504180908</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>20.3210926055908</v>
+        <v>20.3210945129395</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1375" t="n">
-        <v>20.4190292358398</v>
+        <v>20.4190311431885</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1376" t="n">
-        <v>20.2721309661865</v>
+        <v>20.2721290588379</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.4353523254395</v>
+        <v>20.4353504180908</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.6475372314453</v>
+        <v>20.6475391387939</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1387" t="n">
-        <v>21.0882377624512</v>
+        <v>21.0882396697998</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G1388" t="n">
-        <v>20.7944412231445</v>
+        <v>20.7944393157959</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>20.7291469573975</v>
+        <v>20.7291488647461</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G1391" t="n">
-        <v>20.4353523254395</v>
+        <v>20.4353504180908</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1403" t="n">
-        <v>20.8597278594971</v>
+        <v>20.8597259521484</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G1404" t="n">
-        <v>20.7944412231445</v>
+        <v>20.7944393157959</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.5</v>
       </c>
       <c r="G1411" t="n">
-        <v>19.9946537017822</v>
+        <v>19.9946517944336</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1414" t="n">
-        <v>21.0882377624512</v>
+        <v>21.0882396697998</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>21.2841014862061</v>
+        <v>21.2841033935547</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1419" t="n">
-        <v>21.3167476654053</v>
+        <v>21.3167495727539</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1421" t="n">
-        <v>20.4190292358398</v>
+        <v>20.4190311431885</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>24.5</v>
       </c>
       <c r="G1424" t="n">
-        <v>19.9946537017822</v>
+        <v>19.9946517944336</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1425" t="n">
-        <v>20.3537406921387</v>
+        <v>20.35373878479</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1429" t="n">
-        <v>20.2721309661865</v>
+        <v>20.2721290588379</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1430" t="n">
-        <v>20.2721309661865</v>
+        <v>20.2721290588379</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1431" t="n">
-        <v>20.631217956543</v>
+        <v>20.6312160491943</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1432" t="n">
-        <v>20.7291469573975</v>
+        <v>20.7291488647461</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.3210926055908</v>
+        <v>20.3210945129395</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G1438" t="n">
-        <v>19.962007522583</v>
+        <v>19.9620094299316</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1441" t="n">
-        <v>20.6475372314453</v>
+        <v>20.6475391387939</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.9903049468994</v>
+        <v>20.9903030395508</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.9250144958496</v>
+        <v>20.9250164031982</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.7291469573975</v>
+        <v>20.7291488647461</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.2841014862061</v>
+        <v>21.2841033935547</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1449" t="n">
-        <v>20.631217956543</v>
+        <v>20.6312160491943</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1452" t="n">
-        <v>20.3210926055908</v>
+        <v>20.3210945129395</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.5452575683594</v>
+        <v>21.5452556610107</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>26</v>
       </c>
       <c r="G1458" t="n">
-        <v>21.2188148498535</v>
+        <v>21.2188129425049</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1460" t="n">
-        <v>21.0719146728516</v>
+        <v>21.0719127655029</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>21.4636478424072</v>
+        <v>21.4636459350586</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>21.3004264831543</v>
+        <v>21.3004245758057</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>24.7280807495117</v>
+        <v>24.7280788421631</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>25.0545234680176</v>
+        <v>25.0545253753662</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1482" t="n">
-        <v>25.4625778198242</v>
+        <v>25.4625797271729</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>25.5441875457764</v>
+        <v>25.544189453125</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1487" t="n">
-        <v>25.576831817627</v>
+        <v>25.5768337249756</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1488" t="n">
-        <v>25.0545234680176</v>
+        <v>25.0545253753662</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>25.2340660095215</v>
+        <v>25.2340679168701</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1491" t="n">
-        <v>25.5441875457764</v>
+        <v>25.544189453125</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.9609375</v>
+        <v>23.9609355926514</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G1497" t="n">
-        <v>23.944616317749</v>
+        <v>23.9446182250977</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1499" t="n">
-        <v>24.0425491333008</v>
+        <v>24.0425472259521</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1500" t="n">
-        <v>23.7487506866455</v>
+        <v>23.7487525939941</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>29</v>
       </c>
       <c r="G1503" t="n">
-        <v>23.6671390533447</v>
+        <v>23.6671409606934</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G1504" t="n">
-        <v>23.944616317749</v>
+        <v>23.9446182250977</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G1511" t="n">
-        <v>23.1611518859863</v>
+        <v>23.161153793335</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1512" t="n">
-        <v>23.3080501556396</v>
+        <v>23.3080520629883</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>23.1611518859863</v>
+        <v>23.161153793335</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1514" t="n">
-        <v>22.9163188934326</v>
+        <v>22.9163208007812</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G1518" t="n">
-        <v>23.0795402526855</v>
+        <v>23.0795421600342</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G1520" t="n">
-        <v>23.3733425140381</v>
+        <v>23.3733406066895</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G1525" t="n">
-        <v>23.3733425140381</v>
+        <v>23.3733406066895</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1529" t="n">
-        <v>23.3896598815918</v>
+        <v>23.3896617889404</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>21.9533100128174</v>
+        <v>21.953311920166</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.6758346557617</v>
+        <v>21.6758365631104</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.3493938446045</v>
+        <v>21.3493919372559</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1540" t="n">
-        <v>21.2351379394531</v>
+        <v>21.2351398468018</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G1541" t="n">
-        <v>20.7944412231445</v>
+        <v>20.7944393157959</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.6475372314453</v>
+        <v>20.6475391387939</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1547" t="n">
-        <v>21.0719146728516</v>
+        <v>21.0719127655029</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1549" t="n">
-        <v>21.3167476654053</v>
+        <v>21.3167495727539</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1550" t="n">
-        <v>20.631217956543</v>
+        <v>20.6312160491943</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G1563" t="n">
-        <v>19.2764778137207</v>
+        <v>19.2764759063721</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G1564" t="n">
-        <v>19.2764778137207</v>
+        <v>19.2764759063721</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>20.6475372314453</v>
+        <v>20.6475391387939</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1566" t="n">
-        <v>21.6595153808594</v>
+        <v>21.6595134735107</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1582" t="n">
-        <v>24.0425491333008</v>
+        <v>24.0425472259521</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1587" t="n">
-        <v>24.107837677002</v>
+        <v>24.1078395843506</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G1591" t="n">
-        <v>25.2503910064697</v>
+        <v>25.2503890991211</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>25.1687812805176</v>
+        <v>25.1687793731689</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1593" t="n">
-        <v>25.5441875457764</v>
+        <v>25.544189453125</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1594" t="n">
-        <v>25.6584415435791</v>
+        <v>25.6584434509277</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>31.3799991607666</v>
       </c>
       <c r="G1595" t="n">
-        <v>25.6094799041748</v>
+        <v>25.6094779968262</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>31.7199993133545</v>
       </c>
       <c r="G1597" t="n">
-        <v>25.8869552612305</v>
+        <v>25.8869533538818</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1609" t="n">
-        <v>26.8499603271484</v>
+        <v>26.8499622344971</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G1610" t="n">
-        <v>26.4092617034912</v>
+        <v>26.4092636108398</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>31.8799991607666</v>
       </c>
       <c r="G1611" t="n">
-        <v>26.0175285339355</v>
+        <v>26.0175304412842</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>32</v>
       </c>
       <c r="G1612" t="n">
-        <v>26.1154651641846</v>
+        <v>26.1154632568359</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G1617" t="n">
-        <v>24.874979019165</v>
+        <v>24.8749809265137</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>31.5400009155273</v>
       </c>
       <c r="G1619" t="n">
-        <v>25.7400550842285</v>
+        <v>25.7400569915771</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>33.6800003051758</v>
       </c>
       <c r="G1626" t="n">
-        <v>28.2338924407959</v>
+        <v>28.2338943481445</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>34.3199996948242</v>
       </c>
       <c r="G1627" t="n">
-        <v>28.7704048156738</v>
+        <v>28.7704067230225</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G1635" t="n">
-        <v>27.7141494750977</v>
+        <v>27.7141513824463</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1638" t="n">
-        <v>27.8985729217529</v>
+        <v>27.8985748291016</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1646" t="n">
-        <v>24.8471660614014</v>
+        <v>24.84716796875</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1648" t="n">
-        <v>24.8471660614014</v>
+        <v>24.84716796875</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1651" t="n">
-        <v>25.4675064086914</v>
+        <v>25.46750831604</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1653" t="n">
-        <v>24.8471660614014</v>
+        <v>24.84716796875</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G1655" t="n">
-        <v>25.333381652832</v>
+        <v>25.3333797454834</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>25.8195934295654</v>
+        <v>25.8195953369141</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>31.2199993133545</v>
       </c>
       <c r="G1662" t="n">
-        <v>26.1716785430908</v>
+        <v>26.1716804504395</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>30.3600006103516</v>
       </c>
       <c r="G1671" t="n">
-        <v>25.4507427215576</v>
+        <v>25.4507446289062</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>31.0400009155273</v>
       </c>
       <c r="G1672" t="n">
-        <v>26.020788192749</v>
+        <v>26.0207862854004</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G1673" t="n">
-        <v>26.3728713989258</v>
+        <v>26.3728694915771</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G1674" t="n">
-        <v>26.6914234161377</v>
+        <v>26.6914253234863</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1676" t="n">
-        <v>27.2279376983643</v>
+        <v>27.2279357910156</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>34.7200012207031</v>
       </c>
       <c r="G1685" t="n">
-        <v>29.1057243347168</v>
+        <v>29.1057262420654</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>28.8374710083008</v>
+        <v>28.8374691009521</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>34.6199989318848</v>
       </c>
       <c r="G1687" t="n">
-        <v>29.0218925476074</v>
+        <v>29.0218944549561</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>28.5859756469727</v>
+        <v>28.5859775543213</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>35.5800018310547</v>
       </c>
       <c r="G1692" t="n">
-        <v>29.8266658782959</v>
+        <v>29.8266620635986</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>31.6399993896484</v>
       </c>
       <c r="G1696" t="n">
-        <v>26.5237655639648</v>
+        <v>26.5237674713135</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1703" t="n">
-        <v>27.0602760314941</v>
+        <v>27.0602741241455</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>32.8400001525879</v>
       </c>
       <c r="G1710" t="n">
-        <v>27.5297260284424</v>
+        <v>27.5297241210938</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G1711" t="n">
-        <v>27.932107925415</v>
+        <v>27.9321060180664</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1712" t="n">
-        <v>26.6746578216553</v>
+        <v>26.6746597290039</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1717" t="n">
-        <v>23.5394229888916</v>
+        <v>23.5394248962402</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>23.3885288238525</v>
+        <v>23.3885269165039</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G1729" t="n">
-        <v>24.4615535736084</v>
+        <v>24.4615516662598</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1730" t="n">
-        <v>24.6459770202637</v>
+        <v>24.645975112915</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1737" t="n">
-        <v>26.490234375</v>
+        <v>26.4902324676514</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>31.2199993133545</v>
       </c>
       <c r="G1738" t="n">
-        <v>26.1716785430908</v>
+        <v>26.1716804504395</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G1745" t="n">
-        <v>26.6914234161377</v>
+        <v>26.6914253234863</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1746" t="n">
-        <v>26.6746578216553</v>
+        <v>26.6746597290039</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1748" t="n">
-        <v>27.0602760314941</v>
+        <v>27.0602741241455</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>31.0400009155273</v>
       </c>
       <c r="G1751" t="n">
-        <v>26.020788192749</v>
+        <v>26.0207862854004</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1753" t="n">
-        <v>25.7525291442871</v>
+        <v>25.7525310516357</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G1756" t="n">
-        <v>25.6854667663574</v>
+        <v>25.6854648590088</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1758" t="n">
-        <v>24.8136367797852</v>
+        <v>24.8136348724365</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>25.0148258209229</v>
+        <v>25.0148277282715</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>24.9812965393066</v>
+        <v>24.981294631958</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>29.4200000762939</v>
       </c>
       <c r="G1773" t="n">
-        <v>24.6627407073975</v>
+        <v>24.6627426147461</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G1776" t="n">
-        <v>25.0986576080322</v>
+        <v>25.0986595153809</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G1779" t="n">
-        <v>24.3274230957031</v>
+        <v>24.3274250030518</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G1783" t="n">
-        <v>24.495080947876</v>
+        <v>24.4950828552246</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G1784" t="n">
-        <v>24.495080947876</v>
+        <v>24.4950828552246</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>23.8076782226562</v>
+        <v>23.8076801300049</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G1789" t="n">
-        <v>23.0867443084717</v>
+        <v>23.086742401123</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G1791" t="n">
-        <v>23.2879314422607</v>
+        <v>23.2879333496094</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1793" t="n">
-        <v>23.8076782226562</v>
+        <v>23.8076801300049</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1794" t="n">
-        <v>23.7238464355469</v>
+        <v>23.7238483428955</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G1795" t="n">
-        <v>23.7909126281738</v>
+        <v>23.7909107208252</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G1797" t="n">
-        <v>23.271167755127</v>
+        <v>23.2711658477783</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1798" t="n">
-        <v>23.1873359680176</v>
+        <v>23.1873378753662</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1800" t="n">
-        <v>23.7238464355469</v>
+        <v>23.7238483428955</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1801" t="n">
-        <v>23.3717632293701</v>
+        <v>23.3717651367188</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1804" t="n">
-        <v>23.1873359680176</v>
+        <v>23.1873378753662</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>23.3885288238525</v>
+        <v>23.3885269165039</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1806" t="n">
-        <v>23.6232509613037</v>
+        <v>23.6232528686523</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>28.5</v>
       </c>
       <c r="G1809" t="n">
-        <v>23.891508102417</v>
+        <v>23.8915100097656</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>23.9753360748291</v>
+        <v>23.9753379821777</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G1813" t="n">
-        <v>23.4555912017822</v>
+        <v>23.4555931091309</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>28.1599998474121</v>
       </c>
       <c r="G1814" t="n">
-        <v>23.6064872741699</v>
+        <v>23.6064853668213</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G1825" t="n">
-        <v>22.3490390777588</v>
+        <v>22.3490371704102</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1826" t="n">
-        <v>22.7011241912842</v>
+        <v>22.7011222839355</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1833" t="n">
-        <v>21.8963565826416</v>
+        <v>21.8963584899902</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1835" t="n">
-        <v>22.248441696167</v>
+        <v>22.2484436035156</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1839" t="n">
-        <v>22.7346572875977</v>
+        <v>22.734655380249</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1846" t="n">
-        <v>22.935848236084</v>
+        <v>22.9358501434326</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1847" t="n">
-        <v>23.4388275146484</v>
+        <v>23.4388256072998</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1852" t="n">
-        <v>24.1262340545654</v>
+        <v>24.1262321472168</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1853" t="n">
-        <v>24.0591678619385</v>
+        <v>24.0591697692871</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G1859" t="n">
-        <v>22.7681865692139</v>
+        <v>22.7681884765625</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1864" t="n">
-        <v>22.7011241912842</v>
+        <v>22.7011222839355</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1870" t="n">
-        <v>22.2987403869629</v>
+        <v>22.2987422943115</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1871" t="n">
-        <v>22.2987403869629</v>
+        <v>22.2987422943115</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>27.4799995422363</v>
       </c>
       <c r="G1873" t="n">
-        <v>23.0364437103271</v>
+        <v>23.0364418029785</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.935848236084</v>
+        <v>22.9358501434326</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G1877" t="n">
-        <v>23.7070808410645</v>
+        <v>23.7070827484131</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G1878" t="n">
-        <v>23.2879314422607</v>
+        <v>23.2879333496094</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1884" t="n">
-        <v>22.4916095733643</v>
+        <v>22.4916114807129</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G1885" t="n">
-        <v>22.1439800262451</v>
+        <v>22.1439819335938</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>23.2911586761475</v>
+        <v>23.2911567687988</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G1902" t="n">
-        <v>22.5437545776367</v>
+        <v>22.5437564849854</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1907" t="n">
-        <v>22.8044757843018</v>
+        <v>22.8044776916504</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G1913" t="n">
-        <v>23.013053894043</v>
+        <v>23.0130558013916</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G1914" t="n">
-        <v>23.3433036804199</v>
+        <v>23.3433017730713</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1915" t="n">
-        <v>23.0999603271484</v>
+        <v>23.0999622344971</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1918" t="n">
-        <v>23.5518817901611</v>
+        <v>23.5518798828125</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1919" t="n">
-        <v>23.4997386932373</v>
+        <v>23.4997367858887</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1920" t="n">
-        <v>23.7256946563721</v>
+        <v>23.7256927490234</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1923" t="n">
-        <v>23.7430763244629</v>
+        <v>23.7430744171143</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1937" t="n">
-        <v>21.3444347381592</v>
+        <v>21.3444328308105</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1941" t="n">
-        <v>21.1184768676758</v>
+        <v>21.1184749603271</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1943" t="n">
-        <v>20.7013206481934</v>
+        <v>20.7013187408447</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1945" t="n">
-        <v>20.7013206481934</v>
+        <v>20.7013187408447</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1948" t="n">
-        <v>21.7094440460205</v>
+        <v>21.7094459533691</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>25.5</v>
       </c>
       <c r="G1950" t="n">
-        <v>22.1613616943359</v>
+        <v>22.1613636016846</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1959" t="n">
-        <v>21.9354038238525</v>
+        <v>21.9354057312012</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G1960" t="n">
-        <v>21.8832588195801</v>
+        <v>21.8832607269287</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>25.5</v>
       </c>
       <c r="G1961" t="n">
-        <v>22.1613616943359</v>
+        <v>22.1613636016846</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G1966" t="n">
-        <v>21.5703945159912</v>
+        <v>21.5703926086426</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G1968" t="n">
-        <v>20.9098987579346</v>
+        <v>20.9098968505859</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G1969" t="n">
-        <v>20.3536930084229</v>
+        <v>20.3536911010742</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1970" t="n">
-        <v>20.0060634613037</v>
+        <v>20.0060615539551</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1974" t="n">
-        <v>19.2412757873535</v>
+        <v>19.2412776947021</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1975" t="n">
-        <v>18.8415031433105</v>
+        <v>18.8415050506592</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1976" t="n">
-        <v>18.893648147583</v>
+        <v>18.8936500549316</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1980" t="n">
-        <v>19.5193786621094</v>
+        <v>19.519380569458</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1984" t="n">
-        <v>20.2494029998779</v>
+        <v>20.2494010925293</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1986" t="n">
-        <v>20.2667846679688</v>
+        <v>20.2667827606201</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1989" t="n">
-        <v>19.5193786621094</v>
+        <v>19.519380569458</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1990" t="n">
-        <v>19.9191570281982</v>
+        <v>19.9191551208496</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1991" t="n">
-        <v>19.9191570281982</v>
+        <v>19.9191551208496</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1992" t="n">
-        <v>20.2667846679688</v>
+        <v>20.2667827606201</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1997" t="n">
-        <v>20.6839389801025</v>
+        <v>20.6839370727539</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1998" t="n">
-        <v>20.8403720855713</v>
+        <v>20.8403739929199</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G2003" t="n">
-        <v>20.0234451293945</v>
+        <v>20.0234432220459</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G2007" t="n">
-        <v>22.1092185974121</v>
+        <v>22.1092205047607</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G2008" t="n">
-        <v>22.1439800262451</v>
+        <v>22.1439819335938</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G2011" t="n">
-        <v>22.1092185974121</v>
+        <v>22.1092205047607</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G2014" t="n">
-        <v>22.3699398040771</v>
+        <v>22.3699417114258</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G2019" t="n">
-        <v>23.013053894043</v>
+        <v>23.0130558013916</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G2024" t="n">
-        <v>23.013053894043</v>
+        <v>23.0130558013916</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G2025" t="n">
-        <v>22.7523326873779</v>
+        <v>22.7523345947266</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G2026" t="n">
-        <v>23.3954486846924</v>
+        <v>23.3954467773438</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G2027" t="n">
-        <v>24.1428508758545</v>
+        <v>24.1428527832031</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G2030" t="n">
-        <v>24.1428508758545</v>
+        <v>24.1428527832031</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G2034" t="n">
-        <v>24.8728733062744</v>
+        <v>24.8728713989258</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2037" t="n">
-        <v>24.3861904144287</v>
+        <v>24.3861885070801</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>27.4200000762939</v>
       </c>
       <c r="G2038" t="n">
-        <v>23.829984664917</v>
+        <v>23.8299827575684</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G2040" t="n">
-        <v>24.2123775482178</v>
+        <v>24.2123756408691</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G2044" t="n">
-        <v>23.4997386932373</v>
+        <v>23.4997367858887</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G2046" t="n">
-        <v>23.7430763244629</v>
+        <v>23.7430744171143</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G2049" t="n">
-        <v>23.5518817901611</v>
+        <v>23.5518798828125</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G2051" t="n">
-        <v>23.6561698913574</v>
+        <v>23.6561679840088</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G2053" t="n">
-        <v>24.0037994384766</v>
+        <v>24.0037975311279</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G2063" t="n">
-        <v>23.0999603271484</v>
+        <v>23.0999622344971</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G2073" t="n">
-        <v>21.8832588195801</v>
+        <v>21.8832607269287</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G2075" t="n">
-        <v>21.7094440460205</v>
+        <v>21.7094459533691</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>25.5</v>
       </c>
       <c r="G2081" t="n">
-        <v>22.1613616943359</v>
+        <v>22.1613636016846</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G2091" t="n">
-        <v>20.9098987579346</v>
+        <v>20.9098968505859</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G2094" t="n">
-        <v>20.2667846679688</v>
+        <v>20.2667827606201</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G2095" t="n">
-        <v>20.5275077819824</v>
+        <v>20.5275058746338</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G2100" t="n">
-        <v>20.0408248901367</v>
+        <v>20.0408229827881</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2101" t="n">
-        <v>20.2494029998779</v>
+        <v>20.2494010925293</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G2103" t="n">
-        <v>20.0408248901367</v>
+        <v>20.0408229827881</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G2105" t="n">
-        <v>20.5275077819824</v>
+        <v>20.5275058746338</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G2112" t="n">
-        <v>20.9098987579346</v>
+        <v>20.9098968505859</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G2113" t="n">
-        <v>21.1184768676758</v>
+        <v>21.1184749603271</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2124" t="n">
-        <v>22.7697143554688</v>
+        <v>22.7697162628174</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G2126" t="n">
-        <v>23.0999603271484</v>
+        <v>23.0999622344971</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G2129" t="n">
-        <v>23.3954486846924</v>
+        <v>23.3954467773438</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>22.3600006103516</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>362031</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>22.7600002288818</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>22.7600002288818</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
